--- a/output/pdf_financials_xlsx/LTC.xlsx
+++ b/output/pdf_financials_xlsx/LTC.xlsx
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.010287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -829,7 +829,7 @@
         <v>-1.3e-05</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.012191</v>
+        <v>0.001904</v>
       </c>
     </row>
     <row r="30">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>36.28921831279396</v>
+        <v>5.667678752158124</v>
       </c>
     </row>
     <row r="31">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.010287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.012689</v>
       </c>
     </row>
     <row r="119">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3714,7 +3714,11 @@
           <t>Exploration and evaluation expenditures (Note 7)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -4216,7 +4220,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/output/pdf_financials_xlsx/LTC.xlsx
+++ b/output/pdf_financials_xlsx/LTC.xlsx
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000208</v>
       </c>
     </row>
     <row r="13">
@@ -803,7 +803,7 @@
         <v>-1.3e-05</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.001904</v>
+        <v>0.001696</v>
       </c>
     </row>
     <row r="28">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.010287</v>
       </c>
     </row>
     <row r="29">
@@ -829,7 +829,7 @@
         <v>-1.3e-05</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.001904</v>
+        <v>0.011983</v>
       </c>
     </row>
     <row r="30">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5.667678752158124</v>
+        <v>35.67006012978508</v>
       </c>
     </row>
     <row r="31">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.010287</v>
       </c>
     </row>
     <row r="101">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/output/pdf_financials_xlsx/LTC.xlsx
+++ b/output/pdf_financials_xlsx/LTC.xlsx
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.000695</v>
       </c>
     </row>
     <row r="111">
@@ -2297,7 +2297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3470,7 +3470,11 @@
           <t>Accretion (Note 10)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -3526,7 +3530,11 @@
           <t>Deferred income tax expense (Note 13)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -3991,98 +3999,108 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>incorporation,</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>(Cdn$ thousands, except per share amounts) Dec 31, 2025 Dec</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.01315</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Petroleum and natural gas sales (Note 16) $</t>
+          <t>Due to related party (Note 9)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.038142</v>
+      <c r="E63" s="5" t="n">
+        <v>0.768871</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Royalties</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>-0.004548</v>
+          <t>Change in non-cash working capital</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>-0.755721</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REVENUE total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES total</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4090,29 +4108,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>0.033594</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>INCREASE IN CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4120,60 +4140,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>0.000208</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gain on risk management contracts (Note 11)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>CASH AND CASH EQUIVALENTS, BEGINNING OF PERIOD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>0.000735</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Operating</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>CASH AND CASH EQUIVALENTS, END OF PERIOD $</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0.013665</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4184,22 +4218,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>incorporation,</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>(Cdn$ thousands, except per share amounts) Dec 31, 2025 Dec</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.000918</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="70">
@@ -4210,26 +4242,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Depletion, depreciation and amortization (Note 8)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Petroleum and natural gas sales (Note 16) $</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.010287</v>
+        <v>0.038142</v>
       </c>
     </row>
     <row r="71">
@@ -4240,24 +4268,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>1.3e-05</v>
+          <t>Royalties</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.005331</v>
+        <v>-0.004548</v>
       </c>
     </row>
     <row r="72">
@@ -4268,22 +4294,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Interest and financing charges</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>REVENUE total</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0007069999999999999</v>
+        <v>0.033594</v>
       </c>
     </row>
     <row r="73">
@@ -4294,22 +4324,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Transaction costs (Note 6)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.000906</v>
+        <v>0.000208</v>
       </c>
     </row>
     <row r="74">
@@ -4320,12 +4354,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Accretion (Note 10)</t>
+          <t>Gain on risk management contracts (Note 11)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -4335,7 +4369,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.000695</v>
+        <v>0.000735</v>
       </c>
     </row>
     <row r="75">
@@ -4351,7 +4385,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 12)</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -4361,7 +4395,7 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.000124</v>
+        <v>0.013665</v>
       </c>
     </row>
     <row r="76">
@@ -4377,19 +4411,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>1.3e-05</v>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.032633</v>
+        <v>0.000918</v>
       </c>
     </row>
     <row r="77">
@@ -4405,19 +4437,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
+          <t>Depletion, depreciation and amortization (Note 8)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>-1.3e-05</v>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.001904</v>
+        <v>0.010287</v>
       </c>
     </row>
     <row r="78">
@@ -4433,21 +4467,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Deferred income tax expense</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1.3e-05</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.000151</v>
+        <v>0.005331</v>
       </c>
     </row>
     <row r="79">
@@ -4463,19 +4495,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>-1.3e-05</v>
+          <t>Interest and financing charges</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.001753</v>
+        <v>0.0007069999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -4491,15 +4521,267 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>Transaction costs (Note 6)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.000906</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Accretion (Note 10)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.000695</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 12)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.000124</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.032633</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-1.3e-05</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.001904</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Deferred income tax expense</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.000151</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-1.3e-05</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.001753</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
           <t>(1) One Common Share was outstanding for the period from date of incorporation, August 21, 2024 to December</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
         <v>0.002024</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F87" s="5" t="n">
         <v>3.1e-05</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>General and administrative $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>-0.01315</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
